--- a/matching/pages_list.xlsx
+++ b/matching/pages_list.xlsx
@@ -442,12 +442,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -458,12 +459,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>Lang URL (old)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Slug</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Canonical LOC</t>
         </is>
       </c>
     </row>
@@ -483,6 +489,11 @@
           <t>contact</t>
         </is>
       </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/contact.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -500,6 +511,11 @@
           <t>customer-service</t>
         </is>
       </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/customer-service.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -517,6 +533,11 @@
           <t>donate</t>
         </is>
       </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/donate.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -534,6 +555,11 @@
           <t>home</t>
         </is>
       </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -543,12 +569,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/1/login.aspx</t>
+          <t>https://www.phoeniximport.com/en/1/home.aspx</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>login</t>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/home.aspx</t>
         </is>
       </c>
     </row>
@@ -560,12 +591,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/1/newsletter.aspx</t>
+          <t>https://www.phoeniximport.com/en/1/login.aspx</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>newsletter</t>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/login.aspx</t>
         </is>
       </c>
     </row>
@@ -577,29 +613,39 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>https://www.phoeniximport.com/en/1/newsletter.aspx</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>newsletter</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/newsletter.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>https://www.phoeniximport.com/en/1/product-range.aspx</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>product-range</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.phoeniximport.com/en/2/404en.aspx</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>404en</t>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/product-range.aspx</t>
         </is>
       </c>
     </row>
@@ -611,12 +657,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/about-us.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/404en.aspx</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>about-us</t>
+          <t>404en</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/404en.aspx</t>
         </is>
       </c>
     </row>
@@ -628,12 +679,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/bestsellers.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/about-us.aspx</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>bestsellers</t>
+          <t>about-us</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/about-us.aspx</t>
         </is>
       </c>
     </row>
@@ -645,12 +701,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/bulk-wholesale-candles-supplier.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/bestsellers.aspx</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>bulk-wholesale-candles-supplier</t>
+          <t>bestsellers</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/bestsellers.aspx</t>
         </is>
       </c>
     </row>
@@ -662,12 +723,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/candles-wholesaler.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/bulk-wholesale-candles-supplier.aspx</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>candles-wholesaler</t>
+          <t>bulk-wholesale-candles-supplier</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/bulk-wholesale-candles-supplier.aspx</t>
         </is>
       </c>
     </row>
@@ -679,12 +745,17 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/company-details.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/candles-wholesaler.aspx</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>company-details</t>
+          <t>candles-wholesaler</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/candles-wholesaler.aspx</t>
         </is>
       </c>
     </row>
@@ -696,12 +767,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/contact.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/company-details.aspx</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>contact</t>
+          <t>company-details</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/company-details.aspx</t>
         </is>
       </c>
     </row>
@@ -713,12 +789,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/covid-19-service-updates-dpd.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/contact.aspx</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>covid-19-service-updates-dpd</t>
+          <t>contact</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/contact.aspx</t>
         </is>
       </c>
     </row>
@@ -730,12 +811,17 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/customer-service.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/covid-19-service-updates-dpd.aspx</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>customer-service</t>
+          <t>covid-19-service-updates-dpd</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/covid-19-service-updates-dpd.aspx</t>
         </is>
       </c>
     </row>
@@ -747,12 +833,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/discount.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/customer-service.aspx</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>discount</t>
+          <t>customer-service</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/customer-service.aspx</t>
         </is>
       </c>
     </row>
@@ -764,12 +855,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/en-bedrijfsvideo.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/discount.aspx</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>en-bedrijfsvideo</t>
+          <t>discount</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/discount.aspx</t>
         </is>
       </c>
     </row>
@@ -781,12 +877,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/en-certificaten.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/en-bedrijfsvideo.aspx</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>en-certificaten</t>
+          <t>en-bedrijfsvideo</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-bedrijfsvideo.aspx</t>
         </is>
       </c>
     </row>
@@ -798,12 +899,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/en-spirituele-kaarsen.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/en-certificaten.aspx</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>en-spirituele-kaarsen</t>
+          <t>en-certificaten</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-certificaten.aspx</t>
         </is>
       </c>
     </row>
@@ -815,12 +921,17 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/en-vacatures.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/en-spirituele-kaarsen.aspx</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>en-vacatures</t>
+          <t>en-spirituele-kaarsen</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-spirituele-kaarsen.aspx</t>
         </is>
       </c>
     </row>
@@ -832,12 +943,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/en-witte-kaarsen-groothandel.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/en-vacatures.aspx</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>en-witte-kaarsen-groothandel</t>
+          <t>en-vacatures</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-vacatures.aspx</t>
         </is>
       </c>
     </row>
@@ -849,12 +965,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/frequently-asked-questions-faq.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/en-witte-kaarsen-groothandel.aspx</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>frequently-asked-questions-faq</t>
+          <t>en-witte-kaarsen-groothandel</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-witte-kaarsen-groothandel.aspx</t>
         </is>
       </c>
     </row>
@@ -866,12 +987,17 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/general-terms-and-conditions.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/frequently-asked-questions-faq.aspx</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>general-terms-and-conditions</t>
+          <t>frequently-asked-questions-faq</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/frequently-asked-questions-faq.aspx</t>
         </is>
       </c>
     </row>
@@ -883,12 +1009,17 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/new-age-wholesale.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/general-terms-and-conditions.aspx</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>new-age-wholesale</t>
+          <t>general-terms-and-conditions</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/general-terms-and-conditions.aspx</t>
         </is>
       </c>
     </row>
@@ -900,12 +1031,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/newsletter.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/new-age-wholesale.aspx</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>newsletter</t>
+          <t>new-age-wholesale</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/new-age-wholesale.aspx</t>
         </is>
       </c>
     </row>
@@ -917,12 +1053,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/offers-of-the-month.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/newsletter.aspx</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>offers-of-the-month</t>
+          <t>newsletter</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/newsletter.aspx</t>
         </is>
       </c>
     </row>
@@ -934,12 +1075,17 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/payment.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/offers-of-the-month.aspx</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>payment</t>
+          <t>offers-of-the-month</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/offers-of-the-month.aspx</t>
         </is>
       </c>
     </row>
@@ -951,12 +1097,17 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/placing-an-order.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/payment.aspx</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>placing-an-order</t>
+          <t>payment</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/payment.aspx</t>
         </is>
       </c>
     </row>
@@ -968,12 +1119,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/privacy-and-cookie-statement.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/placing-an-order.aspx</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>privacy-and-cookie-statement</t>
+          <t>placing-an-order</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/placing-an-order.aspx</t>
         </is>
       </c>
     </row>
@@ -985,12 +1141,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/proclaimer.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/privacy-and-cookie-statement.aspx</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>proclaimer</t>
+          <t>privacy-and-cookie-statement</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/privacy-and-cookie-statement.aspx</t>
         </is>
       </c>
     </row>
@@ -1002,12 +1163,17 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/report-on-delivery-form.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/proclaimer.aspx</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>report-on-delivery-form</t>
+          <t>proclaimer</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/proclaimer.aspx</t>
         </is>
       </c>
     </row>
@@ -1019,12 +1185,17 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/report-on-delivery.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/report-on-delivery-form.aspx</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>report-on-delivery</t>
+          <t>report-on-delivery-form</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/report-on-delivery-form.aspx</t>
         </is>
       </c>
     </row>
@@ -1036,12 +1207,17 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/shipping-and-delivery.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/report-on-delivery.aspx</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>shipping-and-delivery</t>
+          <t>report-on-delivery</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/report-on-delivery.aspx</t>
         </is>
       </c>
     </row>
@@ -1053,12 +1229,17 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/special-offers.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/shipping-and-delivery.aspx</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>special-offers</t>
+          <t>shipping-and-delivery</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/shipping-and-delivery.aspx</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1251,17 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/stock-notification-and-web-api.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/special-offers.aspx</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>stock-notification-and-web-api</t>
+          <t>special-offers</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/special-offers.aspx</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1273,17 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/stock-notification.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/stock-notification-and-web-api.aspx</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>stock-notification</t>
+          <t>stock-notification-and-web-api</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/stock-notification-and-web-api.aspx</t>
         </is>
       </c>
     </row>
@@ -1104,12 +1295,17 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/sustainable-packaging.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/stock-notification.aspx</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>sustainable-packaging</t>
+          <t>stock-notification</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/stock-notification.aspx</t>
         </is>
       </c>
     </row>
@@ -1121,12 +1317,17 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/testpen.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/sustainable-packaging.aspx</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>testpen</t>
+          <t>sustainable-packaging</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/sustainable-packaging.aspx</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1339,17 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/thank-you-for-registering.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/testpen.aspx</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>thank-you-for-registering</t>
+          <t>testpen</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/testpen.aspx</t>
         </is>
       </c>
     </row>
@@ -1155,12 +1361,17 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/en/2/welcome-to-our-website.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/thank-you-for-registering.aspx</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>welcome-to-our-website</t>
+          <t>thank-you-for-registering</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/thank-you-for-registering.aspx</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1383,39 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
+          <t>https://www.phoeniximport.com/en/2/welcome-to-our-website.aspx</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>welcome-to-our-website</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/welcome-to-our-website.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
           <t>https://www.phoeniximport.com/en/2/yogi-yogini-groothandel.aspx</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>yogi-yogini-groothandel</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/yogi-yogini-groothandel.aspx</t>
         </is>
       </c>
     </row>
@@ -1192,12 +1430,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1208,12 +1447,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>Lang URL (old)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Slug</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Canonical LOC</t>
         </is>
       </c>
     </row>
@@ -1233,6 +1477,11 @@
           <t>kontakt</t>
         </is>
       </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/contact.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1250,6 +1499,11 @@
           <t>kundenservice</t>
         </is>
       </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/customer-service.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1267,6 +1521,11 @@
           <t>spenden</t>
         </is>
       </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/donate.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1284,6 +1543,11 @@
           <t>home</t>
         </is>
       </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1293,12 +1557,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/1/einloggen.aspx</t>
+          <t>https://www.phoeniximport.com/de/1/home.aspx</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>einloggen</t>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/home.aspx</t>
         </is>
       </c>
     </row>
@@ -1310,12 +1579,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/1/newsletter.aspx</t>
+          <t>https://www.phoeniximport.com/de/1/einloggen.aspx</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>newsletter</t>
+          <t>einloggen</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/login.aspx</t>
         </is>
       </c>
     </row>
@@ -1327,29 +1601,39 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>https://www.phoeniximport.com/de/1/newsletter.aspx</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>newsletter</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/newsletter.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>https://www.phoeniximport.com/de/1/sortiment.aspx</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>sortiment</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.phoeniximport.com/en/2/404de.aspx</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>404de</t>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/product-range.aspx</t>
         </is>
       </c>
     </row>
@@ -1361,12 +1645,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/%C3%BCber-uns.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/404de.aspx</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>%C3%BCber-uns</t>
+          <t>404de</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/404en.aspx</t>
         </is>
       </c>
     </row>
@@ -1378,12 +1667,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/bestseller.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/%C3%BCber-uns.aspx</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>bestseller</t>
+          <t>%C3%BCber-uns</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/about-us.aspx</t>
         </is>
       </c>
     </row>
@@ -1395,12 +1689,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/lieferant-fr-kerzen.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/bestseller.aspx</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>lieferant-fr-kerzen</t>
+          <t>bestseller</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/bestsellers.aspx</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1711,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/kerzengrohandel.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/lieferant-fr-kerzen.aspx</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>kerzengrohandel</t>
+          <t>lieferant-fr-kerzen</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/bulk-wholesale-candles-supplier.aspx</t>
         </is>
       </c>
     </row>
@@ -1429,12 +1733,17 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/impressum.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/kerzengrohandel.aspx</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>impressum</t>
+          <t>kerzengrohandel</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/candles-wholesaler.aspx</t>
         </is>
       </c>
     </row>
@@ -1446,12 +1755,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/kontakt.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/impressum.aspx</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>kontakt</t>
+          <t>impressum</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/company-details.aspx</t>
         </is>
       </c>
     </row>
@@ -1463,12 +1777,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/covid-19-service-dpd-updates.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/kontakt.aspx</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>covid-19-service-dpd-updates</t>
+          <t>kontakt</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/contact.aspx</t>
         </is>
       </c>
     </row>
@@ -1480,12 +1799,17 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/kundenservice.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/covid-19-service-dpd-updates.aspx</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>kundenservice</t>
+          <t>covid-19-service-dpd-updates</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/covid-19-service-updates-dpd.aspx</t>
         </is>
       </c>
     </row>
@@ -1497,12 +1821,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/rabatte.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/kundenservice.aspx</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>rabatte</t>
+          <t>kundenservice</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/customer-service.aspx</t>
         </is>
       </c>
     </row>
@@ -1514,12 +1843,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/de-bedrijfsvideo.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/rabatte.aspx</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>de-bedrijfsvideo</t>
+          <t>rabatte</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/discount.aspx</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1865,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/de-certificaten.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/de-bedrijfsvideo.aspx</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>de-certificaten</t>
+          <t>de-bedrijfsvideo</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-bedrijfsvideo.aspx</t>
         </is>
       </c>
     </row>
@@ -1548,12 +1887,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/de-spirituele-kaarsen.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/de-certificaten.aspx</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>de-spirituele-kaarsen</t>
+          <t>de-certificaten</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-certificaten.aspx</t>
         </is>
       </c>
     </row>
@@ -1565,12 +1909,17 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/de-vacatures.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/de-spirituele-kaarsen.aspx</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>de-vacatures</t>
+          <t>de-spirituele-kaarsen</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-spirituele-kaarsen.aspx</t>
         </is>
       </c>
     </row>
@@ -1582,12 +1931,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/de-witte-kaarsen-groothandel.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/de-vacatures.aspx</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>de-witte-kaarsen-groothandel</t>
+          <t>de-vacatures</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-vacatures.aspx</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1953,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/hufig-gestellte-fragen-faq.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/de-witte-kaarsen-groothandel.aspx</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>hufig-gestellte-fragen-faq</t>
+          <t>de-witte-kaarsen-groothandel</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-witte-kaarsen-groothandel.aspx</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1975,17 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/allgemeine-geschftsbedingungen.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/hufig-gestellte-fragen-faq.aspx</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>allgemeine-geschftsbedingungen</t>
+          <t>hufig-gestellte-fragen-faq</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/frequently-asked-questions-faq.aspx</t>
         </is>
       </c>
     </row>
@@ -1633,12 +1997,17 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/new-age-grohandel.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/allgemeine-geschftsbedingungen.aspx</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>new-age-grohandel</t>
+          <t>allgemeine-geschftsbedingungen</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/general-terms-and-conditions.aspx</t>
         </is>
       </c>
     </row>
@@ -1650,12 +2019,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/newsletter.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/new-age-grohandel.aspx</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>newsletter</t>
+          <t>new-age-grohandel</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/new-age-wholesale.aspx</t>
         </is>
       </c>
     </row>
@@ -1667,12 +2041,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/angebote-des-monats.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/newsletter.aspx</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>angebote-des-monats</t>
+          <t>newsletter</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/newsletter.aspx</t>
         </is>
       </c>
     </row>
@@ -1684,12 +2063,17 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/bezahlen.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/angebote-des-monats.aspx</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>bezahlen</t>
+          <t>angebote-des-monats</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/offers-of-the-month.aspx</t>
         </is>
       </c>
     </row>
@@ -1701,12 +2085,17 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/bestellen.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/bezahlen.aspx</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>bestellen</t>
+          <t>bezahlen</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/payment.aspx</t>
         </is>
       </c>
     </row>
@@ -1718,12 +2107,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/datenschutz--und-cookieerklrung.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/bestellen.aspx</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>datenschutz--und-cookieerklrung</t>
+          <t>bestellen</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/placing-an-order.aspx</t>
         </is>
       </c>
     </row>
@@ -1735,12 +2129,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/proclaimer.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/datenschutz--und-cookieerklrung.aspx</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>proclaimer</t>
+          <t>datenschutz--und-cookieerklrung</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/privacy-and-cookie-statement.aspx</t>
         </is>
       </c>
     </row>
@@ -1752,12 +2151,17 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/reklamationsformular.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/proclaimer.aspx</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>reklamationsformular</t>
+          <t>proclaimer</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/proclaimer.aspx</t>
         </is>
       </c>
     </row>
@@ -1769,12 +2173,17 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/reklamation.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/reklamationsformular.aspx</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>reklamation</t>
+          <t>reklamationsformular</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/report-on-delivery-form.aspx</t>
         </is>
       </c>
     </row>
@@ -1786,12 +2195,17 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/versenden-und-lieferzeit.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/reklamation.aspx</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>versenden-und-lieferzeit</t>
+          <t>reklamation</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/report-on-delivery.aspx</t>
         </is>
       </c>
     </row>
@@ -1803,12 +2217,17 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/sonderangebote.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/versenden-und-lieferzeit.aspx</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>sonderangebote</t>
+          <t>versenden-und-lieferzeit</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/shipping-and-delivery.aspx</t>
         </is>
       </c>
     </row>
@@ -1820,12 +2239,17 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/vorratinformation-und-web-api.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/sonderangebote.aspx</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>vorratinformation-und-web-api</t>
+          <t>sonderangebote</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/special-offers.aspx</t>
         </is>
       </c>
     </row>
@@ -1837,12 +2261,17 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/vorratsmeldung.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/vorratinformation-und-web-api.aspx</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>vorratsmeldung</t>
+          <t>vorratinformation-und-web-api</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/stock-notification-and-web-api.aspx</t>
         </is>
       </c>
     </row>
@@ -1854,12 +2283,17 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/nachhaltige-unternehmertum.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/vorratsmeldung.aspx</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>nachhaltige-unternehmertum</t>
+          <t>vorratsmeldung</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/stock-notification.aspx</t>
         </is>
       </c>
     </row>
@@ -1871,12 +2305,17 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/testes.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/nachhaltige-unternehmertum.aspx</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>testes</t>
+          <t>nachhaltige-unternehmertum</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/sustainable-packaging.aspx</t>
         </is>
       </c>
     </row>
@@ -1888,12 +2327,17 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/vielen-dank-fr-ihre-registrierung.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/testes.aspx</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>vielen-dank-fr-ihre-registrierung</t>
+          <t>testes</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/testpen.aspx</t>
         </is>
       </c>
     </row>
@@ -1905,12 +2349,17 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/de/2/willkommen-auf-unserer-webseite.aspx</t>
+          <t>https://www.phoeniximport.com/de/2/vielen-dank-fr-ihre-registrierung.aspx</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>willkommen-auf-unserer-webseite</t>
+          <t>vielen-dank-fr-ihre-registrierung</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/thank-you-for-registering.aspx</t>
         </is>
       </c>
     </row>
@@ -1922,12 +2371,39 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
+          <t>https://www.phoeniximport.com/de/2/willkommen-auf-unserer-webseite.aspx</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>willkommen-auf-unserer-webseite</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/welcome-to-our-website.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
           <t>https://www.phoeniximport.com/de/2/yogi-yogini-groothandel.aspx</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>yogi-yogini-groothandel</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/yogi-yogini-groothandel.aspx</t>
         </is>
       </c>
     </row>
@@ -1942,12 +2418,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1958,12 +2435,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>Lang URL (old)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Slug</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Canonical LOC</t>
         </is>
       </c>
     </row>
@@ -1983,6 +2465,11 @@
           <t>contact</t>
         </is>
       </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/contact.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2000,6 +2487,11 @@
           <t>service-clientle</t>
         </is>
       </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/customer-service.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2017,6 +2509,11 @@
           <t>donations</t>
         </is>
       </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/donate.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2034,6 +2531,11 @@
           <t>accueil</t>
         </is>
       </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2043,12 +2545,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/1/se-connecter.aspx</t>
+          <t>https://www.phoeniximport.com/fr/1/accueil.aspx</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>se-connecter</t>
+          <t>accueil</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/home.aspx</t>
         </is>
       </c>
     </row>
@@ -2060,12 +2567,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/1/newsletter.aspx</t>
+          <t>https://www.phoeniximport.com/fr/1/se-connecter.aspx</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>newsletter</t>
+          <t>se-connecter</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/login.aspx</t>
         </is>
       </c>
     </row>
@@ -2077,29 +2589,39 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>https://www.phoeniximport.com/fr/1/newsletter.aspx</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>newsletter</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/newsletter.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>https://www.phoeniximport.com/fr/1/nos-produits.aspx</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>nos-produits</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.phoeniximport.com/en/2/404fr.aspx</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>404fr</t>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/product-range.aspx</t>
         </is>
       </c>
     </row>
@@ -2111,12 +2633,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/qui-sommes-nous.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/404fr.aspx</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>qui-sommes-nous</t>
+          <t>404fr</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/404en.aspx</t>
         </is>
       </c>
     </row>
@@ -2128,12 +2655,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/les-plus-vendus.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/qui-sommes-nous.aspx</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>les-plus-vendus</t>
+          <t>qui-sommes-nous</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/about-us.aspx</t>
         </is>
       </c>
     </row>
@@ -2145,12 +2677,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/fournisseur-grossiste-de-bougies-en-vrac.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/les-plus-vendus.aspx</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>fournisseur-grossiste-de-bougies-en-vrac</t>
+          <t>les-plus-vendus</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/bestsellers.aspx</t>
         </is>
       </c>
     </row>
@@ -2162,12 +2699,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/vente-en-gros-de-bougies.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/fournisseur-grossiste-de-bougies-en-vrac.aspx</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>vente-en-gros-de-bougies</t>
+          <t>fournisseur-grossiste-de-bougies-en-vrac</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/bulk-wholesale-candles-supplier.aspx</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2721,17 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/informations-sur-la-socit.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/vente-en-gros-de-bougies.aspx</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>informations-sur-la-socit</t>
+          <t>vente-en-gros-de-bougies</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/candles-wholesaler.aspx</t>
         </is>
       </c>
     </row>
@@ -2196,12 +2743,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/contact.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/informations-sur-la-socit.aspx</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>contact</t>
+          <t>informations-sur-la-socit</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/company-details.aspx</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2765,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/mise--jour-dpd-service-mise--jour-corona-virus.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/contact.aspx</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>mise--jour-dpd-service-mise--jour-corona-virus</t>
+          <t>contact</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/contact.aspx</t>
         </is>
       </c>
     </row>
@@ -2230,12 +2787,17 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/service-client%C3%A8le.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/mise--jour-dpd-service-mise--jour-corona-virus.aspx</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>service-client%C3%A8le</t>
+          <t>mise--jour-dpd-service-mise--jour-corona-virus</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/covid-19-service-updates-dpd.aspx</t>
         </is>
       </c>
     </row>
@@ -2247,12 +2809,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/remises.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/service-client%C3%A8le.aspx</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>remises</t>
+          <t>service-client%C3%A8le</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/customer-service.aspx</t>
         </is>
       </c>
     </row>
@@ -2264,12 +2831,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/fr-bedrijfsvideo.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/remises.aspx</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>fr-bedrijfsvideo</t>
+          <t>remises</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/discount.aspx</t>
         </is>
       </c>
     </row>
@@ -2281,12 +2853,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/fr-certificaten.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/fr-bedrijfsvideo.aspx</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>fr-certificaten</t>
+          <t>fr-bedrijfsvideo</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-bedrijfsvideo.aspx</t>
         </is>
       </c>
     </row>
@@ -2298,12 +2875,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/fr-spirituele-kaarsen.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/fr-certificaten.aspx</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>fr-spirituele-kaarsen</t>
+          <t>fr-certificaten</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-certificaten.aspx</t>
         </is>
       </c>
     </row>
@@ -2315,12 +2897,17 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/fr-vacatures.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/fr-spirituele-kaarsen.aspx</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>fr-vacatures</t>
+          <t>fr-spirituele-kaarsen</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-spirituele-kaarsen.aspx</t>
         </is>
       </c>
     </row>
@@ -2332,12 +2919,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/fr-witte-kaarsen-groothandel.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/fr-vacatures.aspx</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>fr-witte-kaarsen-groothandel</t>
+          <t>fr-vacatures</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-vacatures.aspx</t>
         </is>
       </c>
     </row>
@@ -2349,12 +2941,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/foire-aux-questions-faq.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/fr-witte-kaarsen-groothandel.aspx</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>foire-aux-questions-faq</t>
+          <t>fr-witte-kaarsen-groothandel</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-witte-kaarsen-groothandel.aspx</t>
         </is>
       </c>
     </row>
@@ -2366,12 +2963,17 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/termes-et-conditions-gnrales.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/foire-aux-questions-faq.aspx</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>termes-et-conditions-gnrales</t>
+          <t>foire-aux-questions-faq</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/frequently-asked-questions-faq.aspx</t>
         </is>
       </c>
     </row>
@@ -2383,12 +2985,17 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/grossiste-new-age.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/termes-et-conditions-gnrales.aspx</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>grossiste-new-age</t>
+          <t>termes-et-conditions-gnrales</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/general-terms-and-conditions.aspx</t>
         </is>
       </c>
     </row>
@@ -2400,12 +3007,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/newsletter.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/grossiste-new-age.aspx</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>newsletter</t>
+          <t>grossiste-new-age</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/new-age-wholesale.aspx</t>
         </is>
       </c>
     </row>
@@ -2417,12 +3029,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/offres-mensuelles.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/newsletter.aspx</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>offres-mensuelles</t>
+          <t>newsletter</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/newsletter.aspx</t>
         </is>
       </c>
     </row>
@@ -2434,12 +3051,17 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/paiement.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/offres-mensuelles.aspx</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>paiement</t>
+          <t>offres-mensuelles</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/offers-of-the-month.aspx</t>
         </is>
       </c>
     </row>
@@ -2451,12 +3073,17 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/passer-une-commande.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/paiement.aspx</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>passer-une-commande</t>
+          <t>paiement</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/payment.aspx</t>
         </is>
       </c>
     </row>
@@ -2468,12 +3095,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/confidentialit-et-cookie.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/passer-une-commande.aspx</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>confidentialit-et-cookie</t>
+          <t>passer-une-commande</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/placing-an-order.aspx</t>
         </is>
       </c>
     </row>
@@ -2485,12 +3117,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/annonce.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/confidentialit-et-cookie.aspx</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>annonce</t>
+          <t>confidentialit-et-cookie</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/privacy-and-cookie-statement.aspx</t>
         </is>
       </c>
     </row>
@@ -2502,12 +3139,17 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/rapport-sur-la-livraison.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/annonce.aspx</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>rapport-sur-la-livraison</t>
+          <t>annonce</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/proclaimer.aspx</t>
         </is>
       </c>
     </row>
@@ -2519,12 +3161,17 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/confirmation--la-livraison.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/rapport-sur-la-livraison.aspx</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>confirmation--la-livraison</t>
+          <t>rapport-sur-la-livraison</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/report-on-delivery-form.aspx</t>
         </is>
       </c>
     </row>
@@ -2536,12 +3183,17 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/conditions-dexpedition-et-de-livraison.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/confirmation--la-livraison.aspx</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>conditions-dexpedition-et-de-livraison</t>
+          <t>confirmation--la-livraison</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/report-on-delivery.aspx</t>
         </is>
       </c>
     </row>
@@ -2553,12 +3205,17 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/offres-spciales.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/conditions-dexpedition-et-de-livraison.aspx</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>offres-spciales</t>
+          <t>conditions-dexpedition-et-de-livraison</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/shipping-and-delivery.aspx</t>
         </is>
       </c>
     </row>
@@ -2570,12 +3227,17 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/notification-de-stock-et-web-api.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/offres-spciales.aspx</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>notification-de-stock-et-web-api</t>
+          <t>offres-spciales</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/special-offers.aspx</t>
         </is>
       </c>
     </row>
@@ -2587,12 +3249,17 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/gadget-davis-de-rapprovisionnement.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/notification-de-stock-et-web-api.aspx</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>gadget-davis-de-rapprovisionnement</t>
+          <t>notification-de-stock-et-web-api</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/stock-notification-and-web-api.aspx</t>
         </is>
       </c>
     </row>
@@ -2604,12 +3271,17 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/emballage-durable.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/gadget-davis-de-rapprovisionnement.aspx</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>emballage-durable</t>
+          <t>gadget-davis-de-rapprovisionnement</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/stock-notification.aspx</t>
         </is>
       </c>
     </row>
@@ -2621,12 +3293,17 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/testfr.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/emballage-durable.aspx</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>testfr</t>
+          <t>emballage-durable</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/sustainable-packaging.aspx</t>
         </is>
       </c>
     </row>
@@ -2638,12 +3315,17 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/merci-pour-votre-inscription.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/testfr.aspx</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>merci-pour-votre-inscription</t>
+          <t>testfr</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/testpen.aspx</t>
         </is>
       </c>
     </row>
@@ -2655,12 +3337,17 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/fr/2/bienvenue-sur-notre-site-internet.aspx</t>
+          <t>https://www.phoeniximport.com/fr/2/merci-pour-votre-inscription.aspx</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>bienvenue-sur-notre-site-internet</t>
+          <t>merci-pour-votre-inscription</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/thank-you-for-registering.aspx</t>
         </is>
       </c>
     </row>
@@ -2672,12 +3359,39 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
+          <t>https://www.phoeniximport.com/fr/2/bienvenue-sur-notre-site-internet.aspx</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>bienvenue-sur-notre-site-internet</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/welcome-to-our-website.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
           <t>https://www.phoeniximport.com/fr/2/yogi-yogini-groothandel.aspx</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>yogi-yogini-groothandel</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/yogi-yogini-groothandel.aspx</t>
         </is>
       </c>
     </row>
@@ -2692,12 +3406,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2708,12 +3423,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>Lang URL (old)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Slug</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Canonical LOC</t>
         </is>
       </c>
     </row>
@@ -2733,6 +3453,11 @@
           <t>contactos</t>
         </is>
       </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/contact.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -2750,6 +3475,11 @@
           <t>atencin-al-cliente</t>
         </is>
       </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/customer-service.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -2767,6 +3497,11 @@
           <t>donaciones</t>
         </is>
       </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/donate.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -2784,6 +3519,11 @@
           <t>inicio</t>
         </is>
       </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2793,12 +3533,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/1/inicia-sesin.aspx</t>
+          <t>https://www.phoeniximport.com/es/1/inicio.aspx</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>inicia-sesin</t>
+          <t>inicio</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/home.aspx</t>
         </is>
       </c>
     </row>
@@ -2810,12 +3555,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/1/boletn.aspx</t>
+          <t>https://www.phoeniximport.com/es/1/inicia-sesin.aspx</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>boletn</t>
+          <t>inicia-sesin</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/login.aspx</t>
         </is>
       </c>
     </row>
@@ -2827,29 +3577,39 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>https://www.phoeniximport.com/es/1/boletn.aspx</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>boletn</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/newsletter.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>https://www.phoeniximport.com/es/1/catlogo.aspx</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>catlogo</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.phoeniximport.com/en/2/404es.aspx</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>404es</t>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/product-range.aspx</t>
         </is>
       </c>
     </row>
@@ -2861,12 +3621,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/sobre-nosotros.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/404es.aspx</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>sobre-nosotros</t>
+          <t>404es</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/404en.aspx</t>
         </is>
       </c>
     </row>
@@ -2878,12 +3643,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/los-ms-vendidos.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/sobre-nosotros.aspx</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>los-ms-vendidos</t>
+          <t>sobre-nosotros</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/about-us.aspx</t>
         </is>
       </c>
     </row>
@@ -2895,12 +3665,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/proveedor-de-velas-al-por-mayor.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/los-ms-vendidos.aspx</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>proveedor-de-velas-al-por-mayor</t>
+          <t>los-ms-vendidos</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/bestsellers.aspx</t>
         </is>
       </c>
     </row>
@@ -2912,12 +3687,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/venta-al-por-mayor-de-velas.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/proveedor-de-velas-al-por-mayor.aspx</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>venta-al-por-mayor-de-velas</t>
+          <t>proveedor-de-velas-al-por-mayor</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/bulk-wholesale-candles-supplier.aspx</t>
         </is>
       </c>
     </row>
@@ -2929,12 +3709,17 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/informacin-de-la-compaa.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/venta-al-por-mayor-de-velas.aspx</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>informacin-de-la-compaa</t>
+          <t>venta-al-por-mayor-de-velas</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/candles-wholesaler.aspx</t>
         </is>
       </c>
     </row>
@@ -2946,12 +3731,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/contactos.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/informacin-de-la-compaa.aspx</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>contactos</t>
+          <t>informacin-de-la-compaa</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/company-details.aspx</t>
         </is>
       </c>
     </row>
@@ -2963,12 +3753,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/dpd-actualizacin-del-servicio-debido-a-corona-virus.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/contactos.aspx</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>dpd-actualizacin-del-servicio-debido-a-corona-virus</t>
+          <t>contactos</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/contact.aspx</t>
         </is>
       </c>
     </row>
@@ -2980,12 +3775,17 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/atencion-al-cliente.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/dpd-actualizacin-del-servicio-debido-a-corona-virus.aspx</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>atencion-al-cliente</t>
+          <t>dpd-actualizacin-del-servicio-debido-a-corona-virus</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/covid-19-service-updates-dpd.aspx</t>
         </is>
       </c>
     </row>
@@ -2997,12 +3797,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/descuentos.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/atencion-al-cliente.aspx</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>descuentos</t>
+          <t>atencion-al-cliente</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/customer-service.aspx</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3819,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/es-bedrijfsvideo.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/descuentos.aspx</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>es-bedrijfsvideo</t>
+          <t>descuentos</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/discount.aspx</t>
         </is>
       </c>
     </row>
@@ -3031,12 +3841,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/es-certificaten.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/es-bedrijfsvideo.aspx</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>es-certificaten</t>
+          <t>es-bedrijfsvideo</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-bedrijfsvideo.aspx</t>
         </is>
       </c>
     </row>
@@ -3048,12 +3863,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/es-spirituele-kaarsen.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/es-certificaten.aspx</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>es-spirituele-kaarsen</t>
+          <t>es-certificaten</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-certificaten.aspx</t>
         </is>
       </c>
     </row>
@@ -3065,12 +3885,17 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/es-vacatures.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/es-spirituele-kaarsen.aspx</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>es-vacatures</t>
+          <t>es-spirituele-kaarsen</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-spirituele-kaarsen.aspx</t>
         </is>
       </c>
     </row>
@@ -3082,12 +3907,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/es-witte-kaarsen-groothandel.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/es-vacatures.aspx</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>es-witte-kaarsen-groothandel</t>
+          <t>es-vacatures</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-vacatures.aspx</t>
         </is>
       </c>
     </row>
@@ -3099,12 +3929,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/preguntas-frecuentes-faq.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/es-witte-kaarsen-groothandel.aspx</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>preguntas-frecuentes-faq</t>
+          <t>es-witte-kaarsen-groothandel</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-witte-kaarsen-groothandel.aspx</t>
         </is>
       </c>
     </row>
@@ -3116,12 +3951,17 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/trminos-generales-y-condiciones.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/preguntas-frecuentes-faq.aspx</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>trminos-generales-y-condiciones</t>
+          <t>preguntas-frecuentes-faq</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/frequently-asked-questions-faq.aspx</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3973,17 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/new-age-al-por-mayor.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/trminos-generales-y-condiciones.aspx</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>new-age-al-por-mayor</t>
+          <t>trminos-generales-y-condiciones</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/general-terms-and-conditions.aspx</t>
         </is>
       </c>
     </row>
@@ -3150,12 +3995,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/boletn-informativo.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/new-age-al-por-mayor.aspx</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>boletn-informativo</t>
+          <t>new-age-al-por-mayor</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/new-age-wholesale.aspx</t>
         </is>
       </c>
     </row>
@@ -3167,12 +4017,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/ofertas-del-mes.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/boletn-informativo.aspx</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>ofertas-del-mes</t>
+          <t>boletn-informativo</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/newsletter.aspx</t>
         </is>
       </c>
     </row>
@@ -3184,12 +4039,17 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/formas-de-pago.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/ofertas-del-mes.aspx</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>formas-de-pago</t>
+          <t>ofertas-del-mes</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/offers-of-the-month.aspx</t>
         </is>
       </c>
     </row>
@@ -3201,12 +4061,17 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/realizar-un-pedido.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/formas-de-pago.aspx</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>realizar-un-pedido</t>
+          <t>formas-de-pago</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/payment.aspx</t>
         </is>
       </c>
     </row>
@@ -3218,12 +4083,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/politica-de-privacidad-y-cookies.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/realizar-un-pedido.aspx</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>politica-de-privacidad-y-cookies</t>
+          <t>realizar-un-pedido</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/placing-an-order.aspx</t>
         </is>
       </c>
     </row>
@@ -3235,12 +4105,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/aviso.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/politica-de-privacidad-y-cookies.aspx</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>aviso</t>
+          <t>politica-de-privacidad-y-cookies</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/privacy-and-cookie-statement.aspx</t>
         </is>
       </c>
     </row>
@@ -3252,12 +4127,17 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/informe-sobre-la-entrega.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/aviso.aspx</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>informe-sobre-la-entrega</t>
+          <t>aviso</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/proclaimer.aspx</t>
         </is>
       </c>
     </row>
@@ -3269,12 +4149,17 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/reclamaciones.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/informe-sobre-la-entrega.aspx</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>reclamaciones</t>
+          <t>informe-sobre-la-entrega</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/report-on-delivery-form.aspx</t>
         </is>
       </c>
     </row>
@@ -3286,12 +4171,17 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/condiciones-de-entrega.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/reclamaciones.aspx</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>condiciones-de-entrega</t>
+          <t>reclamaciones</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/report-on-delivery.aspx</t>
         </is>
       </c>
     </row>
@@ -3303,12 +4193,17 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/ofertas-especiales.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/condiciones-de-entrega.aspx</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>ofertas-especiales</t>
+          <t>condiciones-de-entrega</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/shipping-and-delivery.aspx</t>
         </is>
       </c>
     </row>
@@ -3320,12 +4215,17 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/notificacin-de-stock-y-web-api.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/ofertas-especiales.aspx</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>notificacin-de-stock-y-web-api</t>
+          <t>ofertas-especiales</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/special-offers.aspx</t>
         </is>
       </c>
     </row>
@@ -3337,12 +4237,17 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/advertencia-para-reposicin.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/notificacin-de-stock-y-web-api.aspx</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>advertencia-para-reposicin</t>
+          <t>notificacin-de-stock-y-web-api</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/stock-notification-and-web-api.aspx</t>
         </is>
       </c>
     </row>
@@ -3354,12 +4259,17 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/dpd-actualizacin-del-servicio-debido-a-corona-virus.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/advertencia-para-reposicin.aspx</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>dpd-actualizacin-del-servicio-debido-a-corona-virus</t>
+          <t>advertencia-para-reposicin</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/stock-notification.aspx</t>
         </is>
       </c>
     </row>
@@ -3371,12 +4281,17 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/testes.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/dpd-actualizacin-del-servicio-debido-a-corona-virus.aspx</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>testes</t>
+          <t>dpd-actualizacin-del-servicio-debido-a-corona-virus</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/sustainable-packaging.aspx</t>
         </is>
       </c>
     </row>
@@ -3388,12 +4303,17 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/gracias-por-su-registro.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/testes.aspx</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>gracias-por-su-registro</t>
+          <t>testes</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/testpen.aspx</t>
         </is>
       </c>
     </row>
@@ -3405,12 +4325,17 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/es/2/bienvenidos-a-nuestro-sitio-web.aspx</t>
+          <t>https://www.phoeniximport.com/es/2/gracias-por-su-registro.aspx</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>bienvenidos-a-nuestro-sitio-web</t>
+          <t>gracias-por-su-registro</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/thank-you-for-registering.aspx</t>
         </is>
       </c>
     </row>
@@ -3422,12 +4347,39 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
+          <t>https://www.phoeniximport.com/es/2/bienvenidos-a-nuestro-sitio-web.aspx</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>bienvenidos-a-nuestro-sitio-web</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/welcome-to-our-website.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
           <t>https://www.phoeniximport.com/es/2/yogi-yogini-groothandel.aspx</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>yogi-yogini-groothandel</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/yogi-yogini-groothandel.aspx</t>
         </is>
       </c>
     </row>
@@ -3442,12 +4394,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3458,12 +4411,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>Lang URL (old)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Slug</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Canonical LOC</t>
         </is>
       </c>
     </row>
@@ -3483,6 +4441,11 @@
           <t>contatti</t>
         </is>
       </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/contact.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -3500,6 +4463,11 @@
           <t>assistenza-clienti</t>
         </is>
       </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/customer-service.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -3517,6 +4485,11 @@
           <t>donazioni</t>
         </is>
       </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/donate.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -3534,6 +4507,11 @@
           <t>home</t>
         </is>
       </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -3543,12 +4521,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/1/login.aspx</t>
+          <t>https://www.phoeniximport.com/it/1/home.aspx</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>login</t>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/home.aspx</t>
         </is>
       </c>
     </row>
@@ -3560,12 +4543,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/1/newsletter.aspx</t>
+          <t>https://www.phoeniximport.com/it/1/login.aspx</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>newsletter</t>
+          <t>login</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/login.aspx</t>
         </is>
       </c>
     </row>
@@ -3577,29 +4565,39 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>https://www.phoeniximport.com/it/1/newsletter.aspx</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>newsletter</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/newsletter.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>https://www.phoeniximport.com/it/1/prodotti.aspx</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>prodotti</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.phoeniximport.com/en/2/404it.aspx</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>404it</t>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/product-range.aspx</t>
         </is>
       </c>
     </row>
@@ -3611,12 +4609,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/chi-siamo.aspx</t>
+          <t>https://www.phoeniximport.com/en/2/404it.aspx</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>chi-siamo</t>
+          <t>404it</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/404en.aspx</t>
         </is>
       </c>
     </row>
@@ -3628,12 +4631,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/i-pi-venduti.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/chi-siamo.aspx</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>i-pi-venduti</t>
+          <t>chi-siamo</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/about-us.aspx</t>
         </is>
       </c>
     </row>
@@ -3645,12 +4653,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/fornitore-di-candele-allingrosso.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/i-pi-venduti.aspx</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>fornitore-di-candele-allingrosso</t>
+          <t>i-pi-venduti</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/bestsellers.aspx</t>
         </is>
       </c>
     </row>
@@ -3662,12 +4675,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/commercio-allingrosso-di-candele.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/fornitore-di-candele-allingrosso.aspx</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>commercio-allingrosso-di-candele</t>
+          <t>fornitore-di-candele-allingrosso</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/bulk-wholesale-candles-supplier.aspx</t>
         </is>
       </c>
     </row>
@@ -3679,12 +4697,17 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/informazioni-aziendaz.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/commercio-allingrosso-di-candele.aspx</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>informazioni-aziendaz</t>
+          <t>commercio-allingrosso-di-candele</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/candles-wholesaler.aspx</t>
         </is>
       </c>
     </row>
@@ -3696,12 +4719,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/contatti.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/informazioni-aziendaz.aspx</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>contatti</t>
+          <t>informazioni-aziendaz</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/company-details.aspx</t>
         </is>
       </c>
     </row>
@@ -3713,12 +4741,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/aggiornamento-dpd-aggiornamento-del-servizio-in-emergenza-corona-virus.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/contatti.aspx</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>aggiornamento-dpd-aggiornamento-del-servizio-in-emergenza-corona-virus</t>
+          <t>contatti</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/contact.aspx</t>
         </is>
       </c>
     </row>
@@ -3730,12 +4763,17 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/servizio-clienti.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/aggiornamento-dpd-aggiornamento-del-servizio-in-emergenza-corona-virus.aspx</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>servizio-clienti</t>
+          <t>aggiornamento-dpd-aggiornamento-del-servizio-in-emergenza-corona-virus</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/covid-19-service-updates-dpd.aspx</t>
         </is>
       </c>
     </row>
@@ -3747,12 +4785,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/sconti.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/servizio-clienti.aspx</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>sconti</t>
+          <t>servizio-clienti</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/customer-service.aspx</t>
         </is>
       </c>
     </row>
@@ -3764,12 +4807,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/it-bedrijfsvideo.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/sconti.aspx</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>it-bedrijfsvideo</t>
+          <t>sconti</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/discount.aspx</t>
         </is>
       </c>
     </row>
@@ -3781,12 +4829,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/it-certificaten.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/it-bedrijfsvideo.aspx</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>it-certificaten</t>
+          <t>it-bedrijfsvideo</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-bedrijfsvideo.aspx</t>
         </is>
       </c>
     </row>
@@ -3798,12 +4851,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/it-spirituele-kaarsen.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/it-certificaten.aspx</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>it-spirituele-kaarsen</t>
+          <t>it-certificaten</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-certificaten.aspx</t>
         </is>
       </c>
     </row>
@@ -3815,12 +4873,17 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/it-vacatures.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/it-spirituele-kaarsen.aspx</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>it-vacatures</t>
+          <t>it-spirituele-kaarsen</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-spirituele-kaarsen.aspx</t>
         </is>
       </c>
     </row>
@@ -3832,12 +4895,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/it-witte-kaarsen-groothandel.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/it-vacatures.aspx</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>it-witte-kaarsen-groothandel</t>
+          <t>it-vacatures</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-vacatures.aspx</t>
         </is>
       </c>
     </row>
@@ -3849,12 +4917,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/domande-frequenti-faq.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/it-witte-kaarsen-groothandel.aspx</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>domande-frequenti-faq</t>
+          <t>it-witte-kaarsen-groothandel</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-witte-kaarsen-groothandel.aspx</t>
         </is>
       </c>
     </row>
@@ -3866,12 +4939,17 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/termini-e-condizioni-generali.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/domande-frequenti-faq.aspx</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>termini-e-condizioni-generali</t>
+          <t>domande-frequenti-faq</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/frequently-asked-questions-faq.aspx</t>
         </is>
       </c>
     </row>
@@ -3883,12 +4961,17 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/new-age-allingrosso.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/termini-e-condizioni-generali.aspx</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>new-age-allingrosso</t>
+          <t>termini-e-condizioni-generali</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/general-terms-and-conditions.aspx</t>
         </is>
       </c>
     </row>
@@ -3900,12 +4983,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/newsletter.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/new-age-allingrosso.aspx</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>newsletter</t>
+          <t>new-age-allingrosso</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/new-age-wholesale.aspx</t>
         </is>
       </c>
     </row>
@@ -3917,12 +5005,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/offerte-del-mese.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/newsletter.aspx</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>offerte-del-mese</t>
+          <t>newsletter</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/newsletter.aspx</t>
         </is>
       </c>
     </row>
@@ -3934,12 +5027,17 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/pagamenti.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/offerte-del-mese.aspx</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>pagamenti</t>
+          <t>offerte-del-mese</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/offers-of-the-month.aspx</t>
         </is>
       </c>
     </row>
@@ -3951,12 +5049,17 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/effetuare-un-ordine.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/pagamenti.aspx</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>effetuare-un-ordine</t>
+          <t>pagamenti</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/payment.aspx</t>
         </is>
       </c>
     </row>
@@ -3968,12 +5071,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/privacy-e-cookie.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/effetuare-un-ordine.aspx</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>privacy-e-cookie</t>
+          <t>effetuare-un-ordine</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/placing-an-order.aspx</t>
         </is>
       </c>
     </row>
@@ -3985,12 +5093,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/avviso.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/privacy-e-cookie.aspx</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>avviso</t>
+          <t>privacy-e-cookie</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/privacy-and-cookie-statement.aspx</t>
         </is>
       </c>
     </row>
@@ -4002,12 +5115,17 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/modulo-reclami.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/avviso.aspx</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>modulo-reclami</t>
+          <t>avviso</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/proclaimer.aspx</t>
         </is>
       </c>
     </row>
@@ -4019,12 +5137,17 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/reclami.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/modulo-reclami.aspx</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>reclami</t>
+          <t>modulo-reclami</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/report-on-delivery-form.aspx</t>
         </is>
       </c>
     </row>
@@ -4036,12 +5159,17 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/spedizione-e-consegna.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/reclami.aspx</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>spedizione-e-consegna</t>
+          <t>reclami</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/report-on-delivery.aspx</t>
         </is>
       </c>
     </row>
@@ -4053,12 +5181,17 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/offerte-speciali.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/spedizione-e-consegna.aspx</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>offerte-speciali</t>
+          <t>spedizione-e-consegna</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/shipping-and-delivery.aspx</t>
         </is>
       </c>
     </row>
@@ -4070,12 +5203,17 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/notifica-stock-e-web-api.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/offerte-speciali.aspx</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>notifica-stock-e-web-api</t>
+          <t>offerte-speciali</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/special-offers.aspx</t>
         </is>
       </c>
     </row>
@@ -4087,12 +5225,17 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/avviso-riassortimento.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/notifica-stock-e-web-api.aspx</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>avviso-riassortimento</t>
+          <t>notifica-stock-e-web-api</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/stock-notification-and-web-api.aspx</t>
         </is>
       </c>
     </row>
@@ -4104,12 +5247,17 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/imballaggio-sostenibile.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/avviso-riassortimento.aspx</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>imballaggio-sostenibile</t>
+          <t>avviso-riassortimento</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/stock-notification.aspx</t>
         </is>
       </c>
     </row>
@@ -4121,12 +5269,17 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/testit.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/imballaggio-sostenibile.aspx</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>testit</t>
+          <t>imballaggio-sostenibile</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/sustainable-packaging.aspx</t>
         </is>
       </c>
     </row>
@@ -4138,12 +5291,17 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/grazie-per-aver-effettuato-la-registrazione.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/testit.aspx</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>grazie-per-aver-effettuato-la-registrazione</t>
+          <t>testit</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/testpen.aspx</t>
         </is>
       </c>
     </row>
@@ -4155,12 +5313,17 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/it/2/benvenuti-sul-nostro-sito.aspx</t>
+          <t>https://www.phoeniximport.com/it/2/grazie-per-aver-effettuato-la-registrazione.aspx</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>benvenuti-sul-nostro-sito</t>
+          <t>grazie-per-aver-effettuato-la-registrazione</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/thank-you-for-registering.aspx</t>
         </is>
       </c>
     </row>
@@ -4172,12 +5335,39 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
+          <t>https://www.phoeniximport.com/it/2/benvenuti-sul-nostro-sito.aspx</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>benvenuti-sul-nostro-sito</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/welcome-to-our-website.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
           <t>https://www.phoeniximport.com/it/2/yogi-yogini-groothandel.aspx</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>yogi-yogini-groothandel</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/yogi-yogini-groothandel.aspx</t>
         </is>
       </c>
     </row>
@@ -4192,12 +5382,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:D44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="80" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="75" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4208,12 +5399,17 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>URL</t>
+          <t>Lang URL (old)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Slug</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Canonical LOC</t>
         </is>
       </c>
     </row>
@@ -4233,6 +5429,11 @@
           <t>contact</t>
         </is>
       </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/contact.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -4250,6 +5451,11 @@
           <t>klantenservice</t>
         </is>
       </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/customer-service.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -4267,6 +5473,11 @@
           <t>doneren</t>
         </is>
       </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/donate.aspx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -4284,6 +5495,11 @@
           <t>home</t>
         </is>
       </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -4293,12 +5509,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/1/inloggen.aspx</t>
+          <t>https://www.phoeniximport.com/nl/1/home.aspx</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>inloggen</t>
+          <t>home</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/home.aspx</t>
         </is>
       </c>
     </row>
@@ -4310,12 +5531,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/1/nieuwsbrief.aspx</t>
+          <t>https://www.phoeniximport.com/nl/1/inloggen.aspx</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>nieuwsbrief</t>
+          <t>inloggen</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/login.aspx</t>
         </is>
       </c>
     </row>
@@ -4327,29 +5553,39 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
+          <t>https://www.phoeniximport.com/nl/1/nieuwsbrief.aspx</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>nieuwsbrief</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/newsletter.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>https://www.phoeniximport.com/nl/1/assortiment.aspx</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>assortiment</t>
         </is>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.phoeniximport.com/nl/2/404.aspx</t>
-        </is>
-      </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>404</t>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/1/product-range.aspx</t>
         </is>
       </c>
     </row>
@@ -4361,12 +5597,17 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/over-ons.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/404.aspx</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>over-ons</t>
+          <t>404</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/404en.aspx</t>
         </is>
       </c>
     </row>
@@ -4378,12 +5619,17 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/bestsellers.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/over-ons.aspx</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>bestsellers</t>
+          <t>over-ons</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/about-us.aspx</t>
         </is>
       </c>
     </row>
@@ -4395,12 +5641,17 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/kaarsen-leverancier-in-bulk.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/bestsellers.aspx</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>kaarsen-leverancier-in-bulk</t>
+          <t>bestsellers</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/bestsellers.aspx</t>
         </is>
       </c>
     </row>
@@ -4412,12 +5663,17 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/kaarsen-groothandel.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/kaarsen-leverancier-in-bulk.aspx</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>kaarsen-groothandel</t>
+          <t>kaarsen-leverancier-in-bulk</t>
+        </is>
+      </c>
+      <c r="D13" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/bulk-wholesale-candles-supplier.aspx</t>
         </is>
       </c>
     </row>
@@ -4429,12 +5685,17 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/bedrijfsgegevens.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/kaarsen-groothandel.aspx</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>bedrijfsgegevens</t>
+          <t>kaarsen-groothandel</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/candles-wholesaler.aspx</t>
         </is>
       </c>
     </row>
@@ -4446,12 +5707,17 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/contact.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/bedrijfsgegevens.aspx</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>contact</t>
+          <t>bedrijfsgegevens</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/company-details.aspx</t>
         </is>
       </c>
     </row>
@@ -4463,12 +5729,17 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/covid-19-dpd-service-updates.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/contact.aspx</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>covid-19-dpd-service-updates</t>
+          <t>contact</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/contact.aspx</t>
         </is>
       </c>
     </row>
@@ -4480,12 +5751,17 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/klantenservice.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/covid-19-dpd-service-updates.aspx</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>klantenservice</t>
+          <t>covid-19-dpd-service-updates</t>
+        </is>
+      </c>
+      <c r="D17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/covid-19-service-updates-dpd.aspx</t>
         </is>
       </c>
     </row>
@@ -4497,12 +5773,17 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/kortingen.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/klantenservice.aspx</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>kortingen</t>
+          <t>klantenservice</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/customer-service.aspx</t>
         </is>
       </c>
     </row>
@@ -4514,12 +5795,17 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/bedrijfsvideo.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/kortingen.aspx</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>bedrijfsvideo</t>
+          <t>kortingen</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/discount.aspx</t>
         </is>
       </c>
     </row>
@@ -4531,12 +5817,17 @@
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/certificaten.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/bedrijfsvideo.aspx</t>
         </is>
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>certificaten</t>
+          <t>bedrijfsvideo</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-bedrijfsvideo.aspx</t>
         </is>
       </c>
     </row>
@@ -4548,12 +5839,17 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/spirituele-kaarsen.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/certificaten.aspx</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>spirituele-kaarsen</t>
+          <t>certificaten</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-certificaten.aspx</t>
         </is>
       </c>
     </row>
@@ -4565,12 +5861,17 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/vacatures.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/spirituele-kaarsen.aspx</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>vacatures</t>
+          <t>spirituele-kaarsen</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-spirituele-kaarsen.aspx</t>
         </is>
       </c>
     </row>
@@ -4582,12 +5883,17 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/witte-kaarsen-groothandel.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/vacatures.aspx</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>witte-kaarsen-groothandel</t>
+          <t>vacatures</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-vacatures.aspx</t>
         </is>
       </c>
     </row>
@@ -4599,12 +5905,17 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/veelgestelde-vragen-faq.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/witte-kaarsen-groothandel.aspx</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>veelgestelde-vragen-faq</t>
+          <t>witte-kaarsen-groothandel</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/en-witte-kaarsen-groothandel.aspx</t>
         </is>
       </c>
     </row>
@@ -4616,12 +5927,17 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/algemene-leveringsvoorwaarden.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/veelgestelde-vragen-faq.aspx</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>algemene-leveringsvoorwaarden</t>
+          <t>veelgestelde-vragen-faq</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/frequently-asked-questions-faq.aspx</t>
         </is>
       </c>
     </row>
@@ -4633,12 +5949,17 @@
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/new-age-groothandel.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/algemene-leveringsvoorwaarden.aspx</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>new-age-groothandel</t>
+          <t>algemene-leveringsvoorwaarden</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/general-terms-and-conditions.aspx</t>
         </is>
       </c>
     </row>
@@ -4650,12 +5971,17 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/nieuwsbrief.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/new-age-groothandel.aspx</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>nieuwsbrief</t>
+          <t>new-age-groothandel</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/new-age-wholesale.aspx</t>
         </is>
       </c>
     </row>
@@ -4667,12 +5993,17 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/maand-aanbieding.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/nieuwsbrief.aspx</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>maand-aanbieding</t>
+          <t>nieuwsbrief</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/newsletter.aspx</t>
         </is>
       </c>
     </row>
@@ -4684,12 +6015,17 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/betalen.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/maand-aanbieding.aspx</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>betalen</t>
+          <t>maand-aanbieding</t>
+        </is>
+      </c>
+      <c r="D29" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/offers-of-the-month.aspx</t>
         </is>
       </c>
     </row>
@@ -4701,12 +6037,17 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/bestellen.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/betalen.aspx</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t>bestellen</t>
+          <t>betalen</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/payment.aspx</t>
         </is>
       </c>
     </row>
@@ -4718,12 +6059,17 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/privacy--en-cookieverklaring.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/bestellen.aspx</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>privacy--en-cookieverklaring</t>
+          <t>bestellen</t>
+        </is>
+      </c>
+      <c r="D31" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/placing-an-order.aspx</t>
         </is>
       </c>
     </row>
@@ -4735,12 +6081,17 @@
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/proclaimer.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/privacy--en-cookieverklaring.aspx</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>proclaimer</t>
+          <t>privacy--en-cookieverklaring</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/privacy-and-cookie-statement.aspx</t>
         </is>
       </c>
     </row>
@@ -4752,12 +6103,17 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/reclamatieformulier.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/proclaimer.aspx</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>reclamatieformulier</t>
+          <t>proclaimer</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/proclaimer.aspx</t>
         </is>
       </c>
     </row>
@@ -4769,12 +6125,17 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/reclamatie.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/reclamatieformulier.aspx</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>reclamatie</t>
+          <t>reclamatieformulier</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/report-on-delivery-form.aspx</t>
         </is>
       </c>
     </row>
@@ -4786,12 +6147,17 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/verzenden-en-levertijd.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/reclamatie.aspx</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>verzenden-en-levertijd</t>
+          <t>reclamatie</t>
+        </is>
+      </c>
+      <c r="D35" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/report-on-delivery.aspx</t>
         </is>
       </c>
     </row>
@@ -4803,12 +6169,17 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/speciale-aanbiedingen.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/verzenden-en-levertijd.aspx</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>speciale-aanbiedingen</t>
+          <t>verzenden-en-levertijd</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/shipping-and-delivery.aspx</t>
         </is>
       </c>
     </row>
@@ -4820,12 +6191,17 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/voorraadnotificatie-en-web-api.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/speciale-aanbiedingen.aspx</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>voorraadnotificatie-en-web-api</t>
+          <t>speciale-aanbiedingen</t>
+        </is>
+      </c>
+      <c r="D37" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/special-offers.aspx</t>
         </is>
       </c>
     </row>
@@ -4837,12 +6213,17 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/voorraadnotificatie.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/voorraadnotificatie-en-web-api.aspx</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>voorraadnotificatie</t>
+          <t>voorraadnotificatie-en-web-api</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/stock-notification-and-web-api.aspx</t>
         </is>
       </c>
     </row>
@@ -4854,12 +6235,17 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/duurzaam-ondernemen.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/voorraadnotificatie.aspx</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>duurzaam-ondernemen</t>
+          <t>voorraadnotificatie</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/stock-notification.aspx</t>
         </is>
       </c>
     </row>
@@ -4871,12 +6257,17 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/pagina-om-dingen-te-testen.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/duurzaam-ondernemen.aspx</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>pagina-om-dingen-te-testen</t>
+          <t>duurzaam-ondernemen</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/sustainable-packaging.aspx</t>
         </is>
       </c>
     </row>
@@ -4888,12 +6279,17 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/bedankt-voor-uw-registratie.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/pagina-om-dingen-te-testen.aspx</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>bedankt-voor-uw-registratie</t>
+          <t>pagina-om-dingen-te-testen</t>
+        </is>
+      </c>
+      <c r="D41" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/testpen.aspx</t>
         </is>
       </c>
     </row>
@@ -4905,12 +6301,17 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>https://www.phoeniximport.com/nl/2/welkom-op-onze-website.aspx</t>
+          <t>https://www.phoeniximport.com/nl/2/bedankt-voor-uw-registratie.aspx</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>welkom-op-onze-website</t>
+          <t>bedankt-voor-uw-registratie</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/thank-you-for-registering.aspx</t>
         </is>
       </c>
     </row>
@@ -4922,12 +6323,39 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
+          <t>https://www.phoeniximport.com/nl/2/welkom-op-onze-website.aspx</t>
+        </is>
+      </c>
+      <c r="C43" s="3" t="inlineStr">
+        <is>
+          <t>welkom-op-onze-website</t>
+        </is>
+      </c>
+      <c r="D43" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/welcome-to-our-website.aspx</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="inlineStr">
+        <is>
           <t>https://www.phoeniximport.com/nl/2/yogi-yogini-groothandel.aspx</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>yogi-yogini-groothandel</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>https://www.phoeniximport.com/en/2/yogi-yogini-groothandel.aspx</t>
         </is>
       </c>
     </row>
